--- a/official.xlsx
+++ b/official.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,7 +509,6 @@
       <c r="G2" t="n">
         <v>9321.43</v>
       </c>
-      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -536,7 +535,6 @@
       <c r="G3" t="n">
         <v>10714.28</v>
       </c>
-      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -563,7 +561,6 @@
       <c r="G4" t="n">
         <v>10714.28</v>
       </c>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -590,7 +587,6 @@
       <c r="G5" t="n">
         <v>10714.28</v>
       </c>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -617,7 +613,6 @@
       <c r="G6" t="n">
         <v>121212</v>
       </c>
-      <c r="H6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/official.xlsx
+++ b/official.xlsx
@@ -7,6 +7,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="MERGE_LOG" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1" iterateDelta="0.0001"/>
@@ -617,4 +618,272 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Timestamp</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>CheckNo</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>RefNo</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>IncomingRow</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-06-10 10:11:05</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CHK:1220813|REF:2992</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1220813</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2992</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Matched existing record</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-06-10 10:11:05</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CHK:1220814|REF:3042</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1220814</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3042</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Matched existing record</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-06-10 10:11:05</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CHK:1220815|REF:3043</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1220815</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3043</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Matched existing record</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-06-10 10:11:05</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>DUP_INCOMING</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CHK:1220815|REF:3043</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1220815</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3043</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Duplicate inside incoming file</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-06-10 10:11:05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CHK:1220816|REF:3044</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1220816</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3044</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Matched existing record</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-06-10 10:11:05</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CHK:1220820|REF:3088</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1220820</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3088</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Matched existing record</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-06-10 10:11:05</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>DUP_INCOMING</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CHK:1220816|REF:3044</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1220816</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3044</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Duplicate inside incoming file</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>